--- a/business_forms/022_market_satisfaction_survey--business_forms.xlsx
+++ b/business_forms/022_market_satisfaction_survey--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>market_satisfaction_survey_page</t>
+          <t>customer_support</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What do you think about the customer support team?</t>
+          <t>Customer Support</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customer_satisfaction_level</t>
+          <t>Customer Satisfaction Level</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -574,11 +574,7 @@
           <t>Product Quality Rating</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Rate our product out of 5 stars.</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -593,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>time_spent_survey</t>
+          <t>time_spent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How much time do you usually spend in our store?</t>
+          <t>Time Spent in Store</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -616,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>overall_satisfaction_rating</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Overall Satisfaction Rating</t>
+          <t>Overall Satisfaction</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -639,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>customer_satisfaction_level_note</t>
+          <t>customer_satisfaction_note</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>customer_satisfaction_level_note</t>
+          <t>Customer Satisfaction Note</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>product_quality_note</t>
+          <t>store_visit_frequency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>product_quality_note</t>
+          <t>Store Visit Frequency</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>store_visit_frequency</t>
+          <t>employee_friendliness</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Store Visit Frequency</t>
+          <t>Employee Friendliness</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,23 +699,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>employee_friendliness</t>
+          <t>other_notes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>employee_friendliness</t>
+          <t>Other Notes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -736,149 +732,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>product_price_range_note</t>
+          <t>Product Price Range Note</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_level_note</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_level_note</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>store_visit_frequency</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Store Visit Frequency</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>employee_friendliness</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>employee_friendliness</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>store_visit_frequency</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Store Visit Frequency</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>employee_friendliness</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>employee_friendliness</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_level_note</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_level_note</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -895,10 +753,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -923,7 +781,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>market_satisfaction_survey_page_choices</t>
+          <t>customer_support_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -940,7 +798,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>market_satisfaction_survey_page_choices</t>
+          <t>customer_support_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -957,7 +815,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>market_satisfaction_survey_page_choices</t>
+          <t>customer_support_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -974,7 +832,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>market_satisfaction_survey_page_choices</t>
+          <t>customer_support_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -991,7 +849,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>market_satisfaction_survey_page_choices</t>
+          <t>customer_support_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1008,7 +866,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>overall_satisfaction_rating_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1025,7 +883,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>overall_satisfaction_rating_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1042,7 +900,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>overall_satisfaction_rating_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1059,7 +917,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>overall_satisfaction_rating_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1076,7 +934,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>overall_satisfaction_rating_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1221,278 +1079,6 @@
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>very unfriendly</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>store_visit_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>often</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>often</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>store_visit_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>occasionally</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>occasionally</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>store_visit_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>employee_friendliness_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>very_friendly</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>very friendly</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>employee_friendliness_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>friendly</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>friendly</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>employee_friendliness_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>employee_friendliness_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>unfriendly</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>unfriendly</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>employee_friendliness_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>very_unfriendly</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>very unfriendly</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>store_visit_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>often</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>often</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>store_visit_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>occasionally</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>occasionally</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>store_visit_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>employee_friendliness_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>very_friendly</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>very friendly</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>employee_friendliness_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>friendly</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>friendly</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>employee_friendliness_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>employee_friendliness_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>unfriendly</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>unfriendly</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>employee_friendliness_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>very_unfriendly</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
         <is>
           <t>very unfriendly</t>
         </is>
